--- a/Figure 6/Figure 6-E.xlsx
+++ b/Figure 6/Figure 6-E.xlsx
@@ -5,27 +5,36 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Wench\Desktop\英文写作\英文写作\工程菌KR32\论文需要上传的数据\图6\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Wench\Desktop\英文写作\英文写作\工程菌KR32\论文需要上传的数据\iMetaOmics20260210\Figure 6\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA17B5F1-D4BC-4683-B572-120C0C02882A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{971FD0BE-7171-4169-BA4B-E427AA6E4C50}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-23260" yWindow="750" windowWidth="19500" windowHeight="15580" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28790" yWindow="4080" windowWidth="16730" windowHeight="15370" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="25">
   <si>
     <t>DLA</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -101,22 +110,6 @@
   </si>
   <si>
     <t>ETEC+WB800_KR32 6</t>
-  </si>
-  <si>
-    <t>CON 7</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ETEC 7</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ETEC+WB800 7</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ETEC+WB800_KR32 7</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -126,7 +119,7 @@
   <numFmts count="1">
     <numFmt numFmtId="176" formatCode="0.00_ "/>
   </numFmts>
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -140,6 +133,18 @@
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -162,12 +167,23 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -450,241 +466,243 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:C28"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="22.33203125" customWidth="1"/>
     <col min="2" max="2" width="8.6640625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="B1" s="1" t="s">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1" s="5"/>
+      <c r="B1" s="6" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+    <row r="2" spans="1:3" ht="15" x14ac:dyDescent="0.3">
+      <c r="A2" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="2">
-        <v>8.4180208000831414</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
+      <c r="B2" s="5">
+        <v>1.2488839607154201</v>
+      </c>
+      <c r="C2" s="3"/>
+    </row>
+    <row r="3" spans="1:3" ht="15" x14ac:dyDescent="0.3">
+      <c r="A3" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="2">
-        <v>13.684851274209233</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
+      <c r="B3" s="5">
+        <v>1.3849687509000299</v>
+      </c>
+      <c r="C3" s="3"/>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="2">
-        <v>14.386353007549495</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
+      <c r="B4" s="5">
+        <v>1.34572736960341</v>
+      </c>
+      <c r="C4" s="4"/>
+    </row>
+    <row r="5" spans="1:3" ht="15" x14ac:dyDescent="0.3">
+      <c r="A5" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="2">
-        <v>9.828447565529169</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
+      <c r="B5" s="5">
+        <v>1.25140404942254</v>
+      </c>
+      <c r="C5" s="3"/>
+    </row>
+    <row r="6" spans="1:3" ht="15" x14ac:dyDescent="0.3">
+      <c r="A6" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="B6" s="2">
-        <v>8.2584198766247745</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
+      <c r="B6" s="5">
+        <v>1.21324270614326</v>
+      </c>
+      <c r="C6" s="3"/>
+    </row>
+    <row r="7" spans="1:3" ht="15" x14ac:dyDescent="0.3">
+      <c r="A7" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="B7" s="2">
-        <v>12.693840889014261</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
-        <v>25</v>
-      </c>
-      <c r="B8" s="2">
-        <v>15.254878963113629</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
+      <c r="B7" s="5">
+        <v>1.1264796520837499</v>
+      </c>
+      <c r="C7" s="3"/>
+    </row>
+    <row r="8" spans="1:3" ht="15" x14ac:dyDescent="0.3">
+      <c r="A8" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="B9" s="2">
-        <v>13.725679417419512</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A10" t="s">
+      <c r="B8" s="5">
+        <v>1.58153567005559</v>
+      </c>
+      <c r="C8" s="3"/>
+    </row>
+    <row r="9" spans="1:3" ht="15" x14ac:dyDescent="0.3">
+      <c r="A9" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="B10" s="2">
-        <v>9.7319446815776001</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A11" t="s">
+      <c r="B9" s="5">
+        <v>1.33888712882693</v>
+      </c>
+      <c r="C9" s="3"/>
+    </row>
+    <row r="10" spans="1:3" ht="15" x14ac:dyDescent="0.3">
+      <c r="A10" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="B11" s="2">
-        <v>14.289850123597926</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A12" t="s">
+      <c r="B10" s="5">
+        <v>1.46705164021774</v>
+      </c>
+      <c r="C10" s="3"/>
+    </row>
+    <row r="11" spans="1:3" ht="15" x14ac:dyDescent="0.3">
+      <c r="A11" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="B12" s="2">
-        <v>10.7600715606001</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A13" t="s">
+      <c r="B11" s="5">
+        <v>1.58873592350451</v>
+      </c>
+      <c r="C11" s="3"/>
+    </row>
+    <row r="12" spans="1:3" ht="15" x14ac:dyDescent="0.3">
+      <c r="A12" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="B13" s="2">
-        <v>14.497702489032076</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A14" t="s">
+      <c r="B12" s="5">
+        <v>1.34968750900032</v>
+      </c>
+      <c r="C12" s="3"/>
+    </row>
+    <row r="13" spans="1:3" ht="15" x14ac:dyDescent="0.3">
+      <c r="A13" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="B14" s="2">
-        <v>15.39592163965823</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A15" t="s">
-        <v>26</v>
-      </c>
-      <c r="B15" s="2">
-        <v>14.805769387800552</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A16" t="s">
+      <c r="B13" s="5">
+        <v>1.5556147576394701</v>
+      </c>
+      <c r="C13" s="3"/>
+    </row>
+    <row r="14" spans="1:3" ht="15" x14ac:dyDescent="0.3">
+      <c r="A14" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="B16" s="2">
-        <v>15.061873195210488</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A17" t="s">
+      <c r="B14" s="5">
+        <v>1.61753693730019</v>
+      </c>
+      <c r="C14" s="3"/>
+    </row>
+    <row r="15" spans="1:3" ht="15" x14ac:dyDescent="0.3">
+      <c r="A15" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="B17" s="2">
-        <v>9.4275894321918781</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A18" t="s">
+      <c r="B15" s="5">
+        <v>1.4760519570288899</v>
+      </c>
+      <c r="C15" s="3"/>
+    </row>
+    <row r="16" spans="1:3" ht="15" x14ac:dyDescent="0.3">
+      <c r="A16" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="B18" s="2">
-        <v>8.4625605926761747</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A19" t="s">
+      <c r="B16" s="5">
+        <v>1.4738918809942101</v>
+      </c>
+      <c r="C16" s="3"/>
+    </row>
+    <row r="17" spans="1:3" ht="15" x14ac:dyDescent="0.3">
+      <c r="A17" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="B19" s="2">
-        <v>7.5680530914327715</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A20" t="s">
+      <c r="B17" s="5">
+        <v>1.2316033524380099</v>
+      </c>
+      <c r="C17" s="3"/>
+    </row>
+    <row r="18" spans="1:3" ht="15" x14ac:dyDescent="0.3">
+      <c r="A18" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="B20" s="2">
-        <v>15.1472411310138</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A21" t="s">
+      <c r="B18" s="5">
+        <v>1.6214970766971</v>
+      </c>
+      <c r="C18" s="3"/>
+    </row>
+    <row r="19" spans="1:3" ht="15" x14ac:dyDescent="0.3">
+      <c r="A19" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="B21" s="2">
-        <v>13.521538701368117</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A22" t="s">
-        <v>27</v>
-      </c>
-      <c r="B22" s="2">
-        <v>11.112678251961608</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A23" t="s">
+      <c r="B19" s="5">
+        <v>1.5563347829843599</v>
+      </c>
+      <c r="C19" s="3"/>
+    </row>
+    <row r="20" spans="1:3" ht="15" x14ac:dyDescent="0.3">
+      <c r="A20" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="B23" s="2">
-        <v>12.697552538397012</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A24" t="s">
+      <c r="B20" s="5">
+        <v>1.50845309754903</v>
+      </c>
+      <c r="C20" s="3"/>
+    </row>
+    <row r="21" spans="1:3" ht="15" x14ac:dyDescent="0.3">
+      <c r="A21" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="B24" s="2">
-        <v>9.3533564445368249</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A25" t="s">
+      <c r="B21" s="5">
+        <v>1.2971256588231901</v>
+      </c>
+      <c r="C21" s="3"/>
+    </row>
+    <row r="22" spans="1:3" ht="15" x14ac:dyDescent="0.3">
+      <c r="A22" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="B25" s="2">
-        <v>14.508837437180333</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A26" t="s">
+      <c r="B22" s="5">
+        <v>1.4573312980616899</v>
+      </c>
+      <c r="C22" s="3"/>
+    </row>
+    <row r="23" spans="1:3" ht="15" x14ac:dyDescent="0.3">
+      <c r="A23" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="B26" s="2">
-        <v>8.5219469828002197</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A27" t="s">
+      <c r="B23" s="5">
+        <v>1.42205005616198</v>
+      </c>
+      <c r="C23" s="3"/>
+    </row>
+    <row r="24" spans="1:3" ht="15" x14ac:dyDescent="0.3">
+      <c r="A24" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="B27" s="2">
-        <v>12.434025432221569</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A28" t="s">
+      <c r="B24" s="5">
+        <v>1.2931655194262801</v>
+      </c>
+      <c r="C24" s="3"/>
+    </row>
+    <row r="25" spans="1:3" ht="15" x14ac:dyDescent="0.3">
+      <c r="A25" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="B28" s="2">
-        <v>11.906971219870686</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A29" t="s">
-        <v>28</v>
-      </c>
-      <c r="B29" s="2">
-        <v>10.904825886527455</v>
-      </c>
+      <c r="B25" s="5">
+        <v>1.4116096886610401</v>
+      </c>
+      <c r="C25" s="3"/>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B26" s="2"/>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B27" s="2"/>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B28" s="2"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
